--- a/EKeeda/DS_April_DEC/Data Science_Curriculum_Plan_DEC_APR.xlsx
+++ b/EKeeda/DS_April_DEC/Data Science_Curriculum_Plan_DEC_APR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training'\DS\EKeeda\DS_April_DEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0CECCF-B449-4821-A665-B87468411500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6157BA7-1BE3-4CC2-9F84-EB62B9B2D070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1045,7 +1045,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1091,6 +1091,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1265,7 +1271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1354,41 +1360,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1408,17 +1389,45 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1676,7 +1685,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="3">
@@ -1685,10 +1694,10 @@
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="30">
         <v>6</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1715,7 +1724,7 @@
       <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:5" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3">
@@ -1724,10 +1733,10 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="30">
         <v>5</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="33" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1776,7 +1785,7 @@
       <c r="E10" s="31"/>
     </row>
     <row r="11" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="3">
@@ -1785,7 +1794,7 @@
       <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="30">
         <v>6</v>
       </c>
       <c r="E11" s="31"/>
@@ -1846,7 +1855,7 @@
       <c r="E16" s="31"/>
     </row>
     <row r="17" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="30" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="3">
@@ -1855,7 +1864,7 @@
       <c r="C17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="30">
         <v>4</v>
       </c>
       <c r="E17" s="31"/>
@@ -1894,7 +1903,7 @@
       <c r="E20" s="32"/>
     </row>
     <row r="21" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="3">
@@ -1903,10 +1912,10 @@
       <c r="C21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="30">
         <v>6</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="30" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1966,7 +1975,7 @@
       <c r="E26" s="32"/>
     </row>
     <row r="27" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="3">
@@ -1975,10 +1984,10 @@
       <c r="C27" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="33">
-        <v>3</v>
-      </c>
-      <c r="E27" s="30" t="s">
+      <c r="D27" s="30">
+        <v>3</v>
+      </c>
+      <c r="E27" s="33" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2005,7 +2014,7 @@
       <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="30" t="s">
         <v>41</v>
       </c>
       <c r="B30" s="3">
@@ -2046,7 +2055,7 @@
       <c r="E32" s="32"/>
     </row>
     <row r="33" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="3">
@@ -2055,10 +2064,10 @@
       <c r="C33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="30">
         <v>6</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="33" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2118,7 +2127,7 @@
       <c r="E38" s="31"/>
     </row>
     <row r="39" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="30" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="3">
@@ -2127,7 +2136,7 @@
       <c r="C39" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="30">
         <v>6</v>
       </c>
       <c r="E39" s="31"/>
@@ -2188,7 +2197,7 @@
       <c r="E44" s="31"/>
     </row>
     <row r="45" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="30" t="s">
         <v>60</v>
       </c>
       <c r="B45" s="3">
@@ -2197,7 +2206,7 @@
       <c r="C45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="30">
         <v>6</v>
       </c>
       <c r="E45" s="31"/>
@@ -2258,7 +2267,7 @@
       <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="33" t="s">
+      <c r="A51" s="30" t="s">
         <v>67</v>
       </c>
       <c r="B51" s="3">
@@ -2267,7 +2276,7 @@
       <c r="C51" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="30">
         <v>6</v>
       </c>
       <c r="E51" s="31"/>
@@ -2295,7 +2304,7 @@
       <c r="E53" s="32"/>
     </row>
     <row r="54" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="30" t="s">
         <v>71</v>
       </c>
       <c r="B54" s="3">
@@ -2304,10 +2313,10 @@
       <c r="C54" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="30">
         <v>6</v>
       </c>
-      <c r="E54" s="33" t="s">
+      <c r="E54" s="30" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2378,7 +2387,7 @@
       <c r="E60" s="32"/>
     </row>
     <row r="61" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="33" t="s">
+      <c r="A61" s="30" t="s">
         <v>80</v>
       </c>
       <c r="B61" s="3">
@@ -2387,10 +2396,10 @@
       <c r="C61" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="33">
+      <c r="D61" s="30">
         <v>6</v>
       </c>
-      <c r="E61" s="33" t="s">
+      <c r="E61" s="30" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2472,7 +2481,7 @@
       <c r="E68" s="32"/>
     </row>
     <row r="69" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33" t="s">
+      <c r="A69" s="30" t="s">
         <v>90</v>
       </c>
       <c r="B69" s="3">
@@ -2484,7 +2493,7 @@
       <c r="D69" s="3">
         <v>3</v>
       </c>
-      <c r="E69" s="30" t="s">
+      <c r="E69" s="33" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2569,7 +2578,7 @@
       <c r="E75" s="31"/>
     </row>
     <row r="76" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="33" t="s">
+      <c r="A76" s="30" t="s">
         <v>100</v>
       </c>
       <c r="B76" s="3">
@@ -2664,7 +2673,7 @@
       <c r="E82" s="32"/>
     </row>
     <row r="83" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="s">
+      <c r="A83" s="30" t="s">
         <v>108</v>
       </c>
       <c r="B83" s="3">
@@ -2673,10 +2682,10 @@
       <c r="C83" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D83" s="33">
+      <c r="D83" s="30">
         <v>6</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="33" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2714,7 +2723,7 @@
       <c r="E86" s="31"/>
     </row>
     <row r="87" spans="1:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="A87" s="33" t="s">
+      <c r="A87" s="30" t="s">
         <v>114</v>
       </c>
       <c r="B87" s="3">
@@ -2770,7 +2779,7 @@
       <c r="E90" s="32"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="33" t="s">
+      <c r="A91" s="30" t="s">
         <v>119</v>
       </c>
       <c r="B91" s="3">
@@ -2779,10 +2788,10 @@
       <c r="C91" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="33">
+      <c r="D91" s="30">
         <v>6</v>
       </c>
-      <c r="E91" s="30" t="s">
+      <c r="E91" s="33" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2853,7 +2862,7 @@
       <c r="E97" s="31"/>
     </row>
     <row r="98" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="33" t="s">
+      <c r="A98" s="30" t="s">
         <v>128</v>
       </c>
       <c r="B98" s="3">
@@ -2862,7 +2871,7 @@
       <c r="C98" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D98" s="33">
+      <c r="D98" s="30">
         <v>3</v>
       </c>
       <c r="E98" s="31"/>
@@ -2890,7 +2899,7 @@
       <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="33" t="s">
+      <c r="A101" s="30" t="s">
         <v>132</v>
       </c>
       <c r="B101" s="3">
@@ -2899,10 +2908,10 @@
       <c r="C101" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D101" s="33">
-        <v>3</v>
-      </c>
-      <c r="E101" s="30" t="s">
+      <c r="D101" s="30">
+        <v>3</v>
+      </c>
+      <c r="E101" s="33" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2929,7 +2938,7 @@
       <c r="E103" s="31"/>
     </row>
     <row r="104" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="33" t="s">
+      <c r="A104" s="30" t="s">
         <v>137</v>
       </c>
       <c r="B104" s="3">
@@ -2938,7 +2947,7 @@
       <c r="C104" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D104" s="33">
+      <c r="D104" s="30">
         <v>6</v>
       </c>
       <c r="E104" s="31"/>
@@ -2988,7 +2997,7 @@
       <c r="E108" s="32"/>
     </row>
     <row r="109" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="33" t="s">
+      <c r="A109" s="30" t="s">
         <v>143</v>
       </c>
       <c r="B109" s="3">
@@ -2997,10 +3006,10 @@
       <c r="C109" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D109" s="33">
+      <c r="D109" s="30">
         <v>6</v>
       </c>
-      <c r="E109" s="30" t="s">
+      <c r="E109" s="33" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3049,7 +3058,7 @@
       <c r="E113" s="31"/>
     </row>
     <row r="114" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="33" t="s">
+      <c r="A114" s="30" t="s">
         <v>150</v>
       </c>
       <c r="B114" s="3">
@@ -3058,7 +3067,7 @@
       <c r="C114" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D114" s="33">
+      <c r="D114" s="30">
         <v>6</v>
       </c>
       <c r="E114" s="31"/>
@@ -3112,7 +3121,7 @@
       <c r="E118" s="32"/>
     </row>
     <row r="119" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="33" t="s">
+      <c r="A119" s="30" t="s">
         <v>156</v>
       </c>
       <c r="B119" s="3">
@@ -3121,10 +3130,10 @@
       <c r="C119" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D119" s="33">
+      <c r="D119" s="30">
         <v>6</v>
       </c>
-      <c r="E119" s="30" t="s">
+      <c r="E119" s="33" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3184,7 +3193,7 @@
       <c r="E124" s="31"/>
     </row>
     <row r="125" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="33" t="s">
+      <c r="A125" s="30" t="s">
         <v>164</v>
       </c>
       <c r="B125" s="3">
@@ -3193,7 +3202,7 @@
       <c r="C125" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D125" s="33">
+      <c r="D125" s="30">
         <v>6</v>
       </c>
       <c r="E125" s="31"/>
@@ -3234,7 +3243,7 @@
       <c r="E128" s="32"/>
     </row>
     <row r="129" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="33" t="s">
+      <c r="A129" s="30" t="s">
         <v>169</v>
       </c>
       <c r="B129" s="3">
@@ -3243,10 +3252,10 @@
       <c r="C129" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D129" s="33">
+      <c r="D129" s="30">
         <v>6</v>
       </c>
-      <c r="E129" s="33" t="s">
+      <c r="E129" s="30" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3273,7 +3282,7 @@
       <c r="E131" s="32"/>
     </row>
     <row r="132" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="33" t="s">
+      <c r="A132" s="30" t="s">
         <v>174</v>
       </c>
       <c r="B132" s="3">
@@ -3285,7 +3294,7 @@
       <c r="D132" s="3">
         <v>5</v>
       </c>
-      <c r="E132" s="30" t="s">
+      <c r="E132" s="33" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3304,54 +3313,6 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="D21:D26"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="D33:D38"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="D6:D10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E32"/>
-    <mergeCell ref="E33:E53"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="E6:E20"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="D119:D124"/>
-    <mergeCell ref="E132:E133"/>
-    <mergeCell ref="E119:E128"/>
-    <mergeCell ref="A125:A128"/>
-    <mergeCell ref="D125:D127"/>
-    <mergeCell ref="D129:D131"/>
-    <mergeCell ref="E129:E131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A119:A124"/>
-    <mergeCell ref="A129:A131"/>
-    <mergeCell ref="D91:D97"/>
-    <mergeCell ref="E91:E100"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="D98:D100"/>
-    <mergeCell ref="A104:A108"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="E101:E108"/>
-    <mergeCell ref="D109:D113"/>
-    <mergeCell ref="E109:E118"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="D104:D108"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A109:A113"/>
-    <mergeCell ref="A61:A68"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A91:A97"/>
-    <mergeCell ref="A76:A81"/>
     <mergeCell ref="E83:E90"/>
     <mergeCell ref="A87:A89"/>
     <mergeCell ref="D83:D86"/>
@@ -3368,6 +3329,54 @@
     <mergeCell ref="E61:E68"/>
     <mergeCell ref="E69:E82"/>
     <mergeCell ref="A54:A60"/>
+    <mergeCell ref="A61:A68"/>
+    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A91:A97"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="E101:E108"/>
+    <mergeCell ref="D109:D113"/>
+    <mergeCell ref="E109:E118"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="D101:D103"/>
+    <mergeCell ref="D104:D108"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A109:A113"/>
+    <mergeCell ref="D91:D97"/>
+    <mergeCell ref="E91:E100"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="D98:D100"/>
+    <mergeCell ref="A104:A108"/>
+    <mergeCell ref="D119:D124"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="E119:E128"/>
+    <mergeCell ref="A125:A128"/>
+    <mergeCell ref="D125:D127"/>
+    <mergeCell ref="D129:D131"/>
+    <mergeCell ref="E129:E131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A119:A124"/>
+    <mergeCell ref="A129:A131"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="E6:E20"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="D21:D26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="D33:D38"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="D6:D10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E32"/>
+    <mergeCell ref="E33:E53"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3438,7 +3447,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49">
+      <c r="A2" s="40">
         <v>1</v>
       </c>
       <c r="B2" s="10">
@@ -3456,16 +3465,16 @@
       <c r="F2" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="52" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="48"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="8">
         <v>44765</v>
       </c>
@@ -3481,14 +3490,14 @@
       <c r="F3" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="35"/>
+      <c r="G3" s="43"/>
       <c r="H3" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="I3" s="48"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:14" ht="23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="8">
         <v>44766</v>
       </c>
@@ -3504,14 +3513,14 @@
       <c r="F4" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="35"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="48"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50">
+      <c r="A5" s="34">
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -3529,7 +3538,7 @@
       <c r="F5" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="53" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="21" t="s">
@@ -3537,7 +3546,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="6" t="s">
         <v>186</v>
       </c>
@@ -3553,13 +3562,13 @@
       <c r="F6" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="53"/>
       <c r="H6" s="21" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="6" t="s">
         <v>187</v>
       </c>
@@ -3575,7 +3584,7 @@
       <c r="F7" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="41" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="21" t="s">
@@ -3583,7 +3592,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50">
+      <c r="A8" s="34">
         <v>3</v>
       </c>
       <c r="B8" s="9">
@@ -3601,13 +3610,13 @@
       <c r="F8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="37"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="21" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="9">
         <v>44720</v>
       </c>
@@ -3623,7 +3632,7 @@
       <c r="F9" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G9" s="37"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="22" t="s">
         <v>240</v>
       </c>
@@ -3648,7 +3657,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="9">
         <v>44750</v>
       </c>
@@ -3664,7 +3673,7 @@
       <c r="F10" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="22" t="s">
@@ -3691,7 +3700,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="50">
+      <c r="A11" s="34">
         <v>4</v>
       </c>
       <c r="B11" s="9">
@@ -3709,7 +3718,7 @@
       <c r="F11" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="22" t="s">
         <v>243</v>
       </c>
@@ -3734,7 +3743,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="6" t="s">
         <v>188</v>
       </c>
@@ -3750,7 +3759,7 @@
       <c r="F12" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="41" t="s">
         <v>247</v>
       </c>
       <c r="H12" s="15" t="s">
@@ -3764,12 +3773,12 @@
       <c r="L12" s="27"/>
       <c r="M12" s="27"/>
       <c r="N12" s="27">
-        <f t="shared" ref="N12:N24" si="0">L12+M12</f>
+        <f t="shared" ref="N12:N22" si="0">L12+M12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="6" t="s">
         <v>189</v>
       </c>
@@ -3785,7 +3794,7 @@
       <c r="F13" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G13" s="37"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="15" t="s">
         <v>248</v>
       </c>
@@ -3802,7 +3811,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50">
+      <c r="A14" s="34">
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3820,7 +3829,7 @@
       <c r="F14" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="47" t="s">
         <v>36</v>
       </c>
       <c r="H14" s="15" t="s">
@@ -3839,7 +3848,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="6" t="s">
         <v>191</v>
       </c>
@@ -3855,7 +3864,7 @@
       <c r="F15" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G15" s="38"/>
+      <c r="G15" s="47"/>
       <c r="H15" s="15" t="s">
         <v>40</v>
       </c>
@@ -3872,7 +3881,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="6" t="s">
         <v>192</v>
       </c>
@@ -3888,7 +3897,7 @@
       <c r="F16" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="41" t="s">
         <v>41</v>
       </c>
       <c r="H16" s="23" t="s">
@@ -3907,7 +3916,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="50">
+      <c r="A17" s="34">
         <v>6</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3925,7 +3934,7 @@
       <c r="F17" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="37"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="23" t="s">
         <v>43</v>
       </c>
@@ -3942,7 +3951,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="6" t="s">
         <v>194</v>
       </c>
@@ -3958,8 +3967,8 @@
       <c r="F18" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="39" t="s">
+      <c r="G18" s="41"/>
+      <c r="H18" s="48" t="s">
         <v>251</v>
       </c>
       <c r="I18" s="27"/>
@@ -3975,7 +3984,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="6" t="s">
         <v>195</v>
       </c>
@@ -3991,8 +4000,8 @@
       <c r="F19" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="49"/>
       <c r="I19" s="27"/>
       <c r="J19" s="27" t="s">
         <v>178</v>
@@ -4006,7 +4015,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="50">
+      <c r="A20" s="34">
         <v>7</v>
       </c>
       <c r="B20" s="9">
@@ -4024,7 +4033,7 @@
       <c r="F20" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G20" s="41" t="s">
         <v>53</v>
       </c>
       <c r="H20" s="24" t="s">
@@ -4051,7 +4060,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="9">
         <v>44629</v>
       </c>
@@ -4067,7 +4076,7 @@
       <c r="F21" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="37"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="24" t="s">
         <v>253</v>
       </c>
@@ -4092,7 +4101,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="9">
         <v>44660</v>
       </c>
@@ -4108,7 +4117,7 @@
       <c r="F22" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G22" s="37" t="s">
+      <c r="G22" s="41" t="s">
         <v>60</v>
       </c>
       <c r="H22" s="24" t="s">
@@ -4141,8 +4150,8 @@
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="52" t="s">
+      <c r="G23" s="41"/>
+      <c r="H23" s="50" t="s">
         <v>255</v>
       </c>
       <c r="I23" s="26">
@@ -4166,7 +4175,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+      <c r="A24" s="34">
         <v>8</v>
       </c>
       <c r="B24" s="9">
@@ -4184,8 +4193,8 @@
       <c r="F24" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="53"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="26">
         <v>44791</v>
       </c>
@@ -4207,7 +4216,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="9">
         <v>44843</v>
       </c>
@@ -4223,7 +4232,7 @@
       <c r="F25" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G25" s="37" t="s">
+      <c r="G25" s="41" t="s">
         <v>71</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -4237,7 +4246,7 @@
       <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="9">
         <v>44874</v>
       </c>
@@ -4253,7 +4262,7 @@
       <c r="F26" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G26" s="37"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="24" t="s">
         <v>259</v>
       </c>
@@ -4265,7 +4274,7 @@
       <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A27" s="50">
+      <c r="A27" s="34">
         <v>9</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -4283,7 +4292,7 @@
       <c r="F27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="G27" s="41" t="s">
         <v>80</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -4297,7 +4306,7 @@
       <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="6" t="s">
         <v>197</v>
       </c>
@@ -4313,7 +4322,7 @@
       <c r="F28" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G28" s="37"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="24" t="s">
         <v>261</v>
       </c>
@@ -4325,7 +4334,7 @@
       <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="6" t="s">
         <v>198</v>
       </c>
@@ -4341,7 +4350,7 @@
       <c r="F29" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G29" s="37" t="s">
+      <c r="G29" s="41" t="s">
         <v>90</v>
       </c>
       <c r="H29" s="24" t="s">
@@ -4355,7 +4364,7 @@
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="50">
+      <c r="A30" s="34">
         <v>10</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -4373,7 +4382,7 @@
       <c r="F30" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="24" t="s">
         <v>93</v>
       </c>
@@ -4385,7 +4394,7 @@
       <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="6" t="s">
         <v>200</v>
       </c>
@@ -4401,7 +4410,7 @@
       <c r="F31" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="24" t="s">
         <v>94</v>
       </c>
@@ -4413,7 +4422,7 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="6" t="s">
         <v>201</v>
       </c>
@@ -4429,7 +4438,7 @@
       <c r="F32" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="35"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="24" t="s">
         <v>95</v>
       </c>
@@ -4441,7 +4450,7 @@
       <c r="N32" s="27"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="50">
+      <c r="A33" s="34">
         <v>11</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -4459,7 +4468,7 @@
       <c r="F33" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="24" t="s">
         <v>96</v>
       </c>
@@ -4471,7 +4480,7 @@
       <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="9">
         <v>44571</v>
       </c>
@@ -4487,7 +4496,7 @@
       <c r="F34" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="43"/>
       <c r="H34" s="24" t="s">
         <v>97</v>
       </c>
@@ -4499,7 +4508,7 @@
       <c r="N34" s="27"/>
     </row>
     <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="9">
         <v>44602</v>
       </c>
@@ -4529,7 +4538,7 @@
       <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="50">
+      <c r="A36" s="34">
         <v>12</v>
       </c>
       <c r="B36" s="9">
@@ -4547,7 +4556,7 @@
       <c r="F36" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G36" s="37" t="s">
+      <c r="G36" s="41" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="24" t="s">
@@ -4561,7 +4570,7 @@
       <c r="N36" s="27"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
+      <c r="A37" s="34"/>
       <c r="B37" s="9">
         <v>44783</v>
       </c>
@@ -4577,7 +4586,7 @@
       <c r="F37" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G37" s="37"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="24" t="s">
         <v>273</v>
       </c>
@@ -4589,7 +4598,7 @@
       <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="9">
         <v>44814</v>
       </c>
@@ -4605,7 +4614,7 @@
       <c r="F38" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="37"/>
+      <c r="G38" s="41"/>
       <c r="H38" s="24" t="s">
         <v>104</v>
       </c>
@@ -4617,7 +4626,7 @@
       <c r="N38" s="27"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="50">
+      <c r="A39" s="34">
         <v>13</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -4635,7 +4644,7 @@
       <c r="F39" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="24" t="s">
         <v>105</v>
       </c>
@@ -4647,7 +4656,7 @@
       <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+      <c r="A40" s="34"/>
       <c r="B40" s="6" t="s">
         <v>204</v>
       </c>
@@ -4663,7 +4672,7 @@
       <c r="F40" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G40" s="37"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="24" t="s">
         <v>106</v>
       </c>
@@ -4675,7 +4684,7 @@
       <c r="N40" s="27"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+      <c r="A41" s="34"/>
       <c r="B41" s="6" t="s">
         <v>205</v>
       </c>
@@ -4691,7 +4700,7 @@
       <c r="F41" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G41" s="37"/>
+      <c r="G41" s="41"/>
       <c r="H41" s="24" t="s">
         <v>102</v>
       </c>
@@ -4703,7 +4712,7 @@
       <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="50">
+      <c r="A42" s="34">
         <v>14</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -4721,10 +4730,10 @@
       <c r="F42" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="41" t="s">
+      <c r="G42" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="H42" s="42" t="s">
+      <c r="H42" s="45" t="s">
         <v>263</v>
       </c>
       <c r="I42" s="27"/>
@@ -4735,7 +4744,7 @@
       <c r="N42" s="27"/>
     </row>
     <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
+      <c r="A43" s="34"/>
       <c r="B43" s="6" t="s">
         <v>207</v>
       </c>
@@ -4751,8 +4760,8 @@
       <c r="F43" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G43" s="41"/>
-      <c r="H43" s="43"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="46"/>
       <c r="I43" s="27"/>
       <c r="J43" s="27"/>
       <c r="K43" s="27"/>
@@ -4761,7 +4770,7 @@
       <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+      <c r="A44" s="34"/>
       <c r="B44" s="6" t="s">
         <v>208</v>
       </c>
@@ -4777,7 +4786,7 @@
       <c r="F44" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G44" s="37" t="s">
+      <c r="G44" s="41" t="s">
         <v>108</v>
       </c>
       <c r="H44" s="24" t="s">
@@ -4791,7 +4800,7 @@
       <c r="N44" s="27"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="50">
+      <c r="A45" s="34">
         <v>15</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -4809,7 +4818,7 @@
       <c r="F45" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G45" s="37"/>
+      <c r="G45" s="41"/>
       <c r="H45" s="24" t="s">
         <v>265</v>
       </c>
@@ -4821,7 +4830,7 @@
       <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
+      <c r="A46" s="34"/>
       <c r="B46" s="6" t="s">
         <v>210</v>
       </c>
@@ -4837,7 +4846,7 @@
       <c r="F46" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="41" t="s">
         <v>114</v>
       </c>
       <c r="H46" s="24" t="s">
@@ -4851,7 +4860,7 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="50"/>
+      <c r="A47" s="34"/>
       <c r="B47" s="6" t="s">
         <v>211</v>
       </c>
@@ -4867,7 +4876,7 @@
       <c r="F47" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G47" s="37"/>
+      <c r="G47" s="41"/>
       <c r="H47" s="24" t="s">
         <v>117</v>
       </c>
@@ -4879,7 +4888,7 @@
       <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="50">
+      <c r="A48" s="34">
         <v>16</v>
       </c>
       <c r="B48" s="9">
@@ -4897,7 +4906,7 @@
       <c r="F48" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G48" s="37"/>
+      <c r="G48" s="41"/>
       <c r="H48" s="24" t="s">
         <v>116</v>
       </c>
@@ -4909,7 +4918,7 @@
       <c r="N48" s="27"/>
     </row>
     <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
+      <c r="A49" s="34"/>
       <c r="B49" s="9">
         <v>44692</v>
       </c>
@@ -4939,7 +4948,7 @@
       <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
+      <c r="A50" s="34"/>
       <c r="B50" s="9">
         <v>44723</v>
       </c>
@@ -4955,7 +4964,7 @@
       <c r="F50" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="G50" s="41" t="s">
         <v>268</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -4969,7 +4978,7 @@
       <c r="N50" s="27"/>
     </row>
     <row r="51" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="50">
+      <c r="A51" s="34">
         <v>17</v>
       </c>
       <c r="B51" s="9">
@@ -4987,8 +4996,8 @@
       <c r="F51" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G51" s="37"/>
-      <c r="H51" s="24" t="s">
+      <c r="G51" s="41"/>
+      <c r="H51" s="54" t="s">
         <v>269</v>
       </c>
       <c r="I51" s="27"/>
@@ -4999,7 +5008,7 @@
       <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
+      <c r="A52" s="34"/>
       <c r="B52" s="9">
         <v>44906</v>
       </c>
@@ -5015,8 +5024,8 @@
       <c r="F52" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G52" s="37"/>
-      <c r="H52" s="24" t="s">
+      <c r="G52" s="41"/>
+      <c r="H52" s="54" t="s">
         <v>166</v>
       </c>
       <c r="I52" s="27"/>
@@ -5027,7 +5036,7 @@
       <c r="N52" s="27"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
+      <c r="A53" s="34"/>
       <c r="B53" s="6" t="s">
         <v>212</v>
       </c>
@@ -5043,8 +5052,8 @@
       <c r="F53" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G53" s="37"/>
-      <c r="H53" s="24" t="s">
+      <c r="G53" s="41"/>
+      <c r="H53" s="54" t="s">
         <v>167</v>
       </c>
       <c r="I53" s="27"/>
@@ -5055,7 +5064,7 @@
       <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="50">
+      <c r="A54" s="34">
         <v>18</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -5073,10 +5082,10 @@
       <c r="F54" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G54" s="37" t="s">
+      <c r="G54" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="H54" s="24" t="s">
+      <c r="H54" s="54" t="s">
         <v>272</v>
       </c>
       <c r="I54" s="27"/>
@@ -5087,7 +5096,7 @@
       <c r="N54" s="27"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="6" t="s">
         <v>214</v>
       </c>
@@ -5103,8 +5112,8 @@
       <c r="F55" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G55" s="37"/>
-      <c r="H55" s="24" t="s">
+      <c r="G55" s="41"/>
+      <c r="H55" s="54" t="s">
         <v>274</v>
       </c>
       <c r="I55" s="27"/>
@@ -5115,7 +5124,7 @@
       <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="6" t="s">
         <v>215</v>
       </c>
@@ -5131,8 +5140,8 @@
       <c r="F56" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G56" s="37"/>
-      <c r="H56" s="24" t="s">
+      <c r="G56" s="41"/>
+      <c r="H56" s="54" t="s">
         <v>279</v>
       </c>
       <c r="I56" s="27"/>
@@ -5143,7 +5152,7 @@
       <c r="N56" s="27"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="50">
+      <c r="A57" s="34">
         <v>19</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -5161,7 +5170,7 @@
       <c r="F57" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G57" s="37"/>
+      <c r="G57" s="41"/>
       <c r="H57" s="15"/>
       <c r="I57" s="27"/>
       <c r="J57" s="27"/>
@@ -5171,7 +5180,7 @@
       <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="6" t="s">
         <v>217</v>
       </c>
@@ -5201,7 +5210,7 @@
       <c r="N58" s="27"/>
     </row>
     <row r="59" spans="1:14" ht="28" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
+      <c r="A59" s="34"/>
       <c r="B59" s="6" t="s">
         <v>218</v>
       </c>
@@ -5231,7 +5240,7 @@
       <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="50">
+      <c r="A60" s="34">
         <v>20</v>
       </c>
       <c r="B60" s="9">
@@ -5249,7 +5258,7 @@
       <c r="F60" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G60" s="37" t="s">
+      <c r="G60" s="41" t="s">
         <v>67</v>
       </c>
       <c r="H60" s="15" t="s">
@@ -5263,7 +5272,7 @@
       <c r="N60" s="27"/>
     </row>
     <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
+      <c r="A61" s="34"/>
       <c r="B61" s="9">
         <v>44632</v>
       </c>
@@ -5279,7 +5288,7 @@
       <c r="F61" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G61" s="37"/>
+      <c r="G61" s="41"/>
       <c r="H61" s="15" t="s">
         <v>70</v>
       </c>
@@ -5291,7 +5300,7 @@
       <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
+      <c r="A62" s="34"/>
       <c r="B62" s="9">
         <v>44663</v>
       </c>
@@ -5307,7 +5316,7 @@
       <c r="F62" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G62" s="37" t="s">
+      <c r="G62" s="41" t="s">
         <v>119</v>
       </c>
       <c r="H62" s="15" t="s">
@@ -5321,7 +5330,7 @@
       <c r="N62" s="27"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="50">
+      <c r="A63" s="34">
         <v>21</v>
       </c>
       <c r="B63" s="9">
@@ -5339,7 +5348,7 @@
       <c r="F63" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G63" s="37"/>
+      <c r="G63" s="41"/>
       <c r="H63" s="15" t="s">
         <v>278</v>
       </c>
@@ -5351,7 +5360,7 @@
       <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
+      <c r="A64" s="34"/>
       <c r="B64" s="9">
         <v>44846</v>
       </c>
@@ -5381,7 +5390,7 @@
       <c r="N64" s="27"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
+      <c r="A65" s="34"/>
       <c r="B65" s="9">
         <v>44877</v>
       </c>
@@ -5411,7 +5420,7 @@
       <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="50">
+      <c r="A66" s="34">
         <v>22</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5429,7 +5438,7 @@
       <c r="F66" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="37" t="s">
+      <c r="G66" s="41" t="s">
         <v>137</v>
       </c>
       <c r="H66" s="15" t="s">
@@ -5443,7 +5452,7 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
+      <c r="A67" s="34"/>
       <c r="B67" s="6" t="s">
         <v>220</v>
       </c>
@@ -5459,7 +5468,7 @@
       <c r="F67" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G67" s="37"/>
+      <c r="G67" s="41"/>
       <c r="H67" s="15" t="s">
         <v>282</v>
       </c>
@@ -5471,7 +5480,7 @@
       <c r="N67" s="27"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
+      <c r="A68" s="34"/>
       <c r="B68" s="6" t="s">
         <v>221</v>
       </c>
@@ -5487,7 +5496,7 @@
       <c r="F68" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G68" s="37"/>
+      <c r="G68" s="41"/>
       <c r="H68" s="15" t="s">
         <v>283</v>
       </c>
@@ -5499,7 +5508,7 @@
       <c r="N68" s="27"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="50">
+      <c r="A69" s="34">
         <v>23</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -5517,7 +5526,7 @@
       <c r="F69" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G69" s="37" t="s">
+      <c r="G69" s="41" t="s">
         <v>143</v>
       </c>
       <c r="H69" s="15" t="s">
@@ -5531,7 +5540,7 @@
       <c r="N69" s="27"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="50"/>
+      <c r="A70" s="34"/>
       <c r="B70" s="6" t="s">
         <v>223</v>
       </c>
@@ -5547,7 +5556,7 @@
       <c r="F70" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G70" s="37"/>
+      <c r="G70" s="41"/>
       <c r="H70" s="15" t="s">
         <v>285</v>
       </c>
@@ -5559,7 +5568,7 @@
       <c r="N70" s="27"/>
     </row>
     <row r="71" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
+      <c r="A71" s="34"/>
       <c r="B71" s="6" t="s">
         <v>224</v>
       </c>
@@ -5575,7 +5584,7 @@
       <c r="F71" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="37" t="s">
+      <c r="G71" s="41" t="s">
         <v>150</v>
       </c>
       <c r="H71" s="15" t="s">
@@ -5589,7 +5598,7 @@
       <c r="N71" s="27"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="50">
+      <c r="A72" s="34">
         <v>24</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -5607,7 +5616,7 @@
       <c r="F72" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G72" s="37"/>
+      <c r="G72" s="41"/>
       <c r="H72" s="15" t="s">
         <v>287</v>
       </c>
@@ -5619,7 +5628,7 @@
       <c r="N72" s="27"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="6" t="s">
         <v>226</v>
       </c>
@@ -5649,7 +5658,7 @@
       <c r="N73" s="27"/>
     </row>
     <row r="74" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="9">
         <v>44927</v>
       </c>
@@ -5665,7 +5674,7 @@
       <c r="F74" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G74" s="51" t="s">
+      <c r="G74" s="42" t="s">
         <v>156</v>
       </c>
       <c r="H74" s="15" t="s">
@@ -5679,7 +5688,7 @@
       <c r="N74" s="27"/>
     </row>
     <row r="75" spans="1:14" ht="23" x14ac:dyDescent="0.25">
-      <c r="A75" s="50">
+      <c r="A75" s="34">
         <v>25</v>
       </c>
       <c r="B75" s="9">
@@ -5697,7 +5706,7 @@
       <c r="F75" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G75" s="51"/>
+      <c r="G75" s="42"/>
       <c r="H75" s="15" t="s">
         <v>291</v>
       </c>
@@ -5709,7 +5718,7 @@
       <c r="N75" s="27"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
+      <c r="A76" s="34"/>
       <c r="B76" s="9">
         <v>45108</v>
       </c>
@@ -5725,7 +5734,7 @@
       <c r="F76" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G76" s="37" t="s">
+      <c r="G76" s="41" t="s">
         <v>169</v>
       </c>
       <c r="H76" s="15" t="s">
@@ -5739,7 +5748,7 @@
       <c r="N76" s="27"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
+      <c r="A77" s="34"/>
       <c r="B77" s="9">
         <v>45139</v>
       </c>
@@ -5755,7 +5764,7 @@
       <c r="F77" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G77" s="35"/>
+      <c r="G77" s="43"/>
       <c r="H77" s="15" t="s">
         <v>172</v>
       </c>
@@ -5767,7 +5776,7 @@
       <c r="N77" s="27"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="50">
+      <c r="A78" s="34">
         <v>26</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -5785,7 +5794,7 @@
       <c r="F78" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G78" s="35"/>
+      <c r="G78" s="43"/>
       <c r="H78" s="15" t="s">
         <v>173</v>
       </c>
@@ -5797,7 +5806,7 @@
       <c r="N78" s="27"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="50"/>
+      <c r="A79" s="34"/>
       <c r="B79" s="6" t="s">
         <v>228</v>
       </c>
@@ -5813,10 +5822,10 @@
       <c r="F79" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G79" s="47" t="s">
+      <c r="G79" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="H79" s="47" t="s">
+      <c r="H79" s="38" t="s">
         <v>175</v>
       </c>
       <c r="I79" s="27"/>
@@ -5827,7 +5836,7 @@
       <c r="N79" s="27"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="50"/>
+      <c r="A80" s="34"/>
       <c r="B80" s="6" t="s">
         <v>229</v>
       </c>
@@ -5843,8 +5852,8 @@
       <c r="F80" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
       <c r="I80" s="27"/>
       <c r="J80" s="27"/>
       <c r="K80" s="27"/>
@@ -5853,7 +5862,7 @@
       <c r="N80" s="27"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="50">
+      <c r="A81" s="34">
         <v>27</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -5871,8 +5880,8 @@
       <c r="F81" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G81" s="47"/>
-      <c r="H81" s="44" t="s">
+      <c r="G81" s="38"/>
+      <c r="H81" s="35" t="s">
         <v>295</v>
       </c>
       <c r="I81" s="27"/>
@@ -5883,7 +5892,7 @@
       <c r="N81" s="27"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="50"/>
+      <c r="A82" s="34"/>
       <c r="B82" s="6" t="s">
         <v>292</v>
       </c>
@@ -5899,8 +5908,8 @@
       <c r="F82" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G82" s="47"/>
-      <c r="H82" s="45"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="36"/>
       <c r="I82" s="27"/>
       <c r="J82" s="27"/>
       <c r="K82" s="27"/>
@@ -5909,7 +5918,7 @@
       <c r="N82" s="27"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="50"/>
+      <c r="A83" s="34"/>
       <c r="B83" s="6" t="s">
         <v>293</v>
       </c>
@@ -5925,8 +5934,8 @@
       <c r="F83" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G83" s="47"/>
-      <c r="H83" s="46"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="37"/>
       <c r="I83" s="27"/>
       <c r="J83" s="27"/>
       <c r="K83" s="27"/>
@@ -5936,26 +5945,29 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="G36:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="G29:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="G50:G53"/>
+    <mergeCell ref="G54:G57"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G48"/>
     <mergeCell ref="H81:H83"/>
     <mergeCell ref="H79:H80"/>
     <mergeCell ref="I2:I4"/>
@@ -5972,29 +5984,26 @@
     <mergeCell ref="G79:G83"/>
     <mergeCell ref="G60:G61"/>
     <mergeCell ref="G62:G63"/>
-    <mergeCell ref="G66:G68"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="G50:G53"/>
-    <mergeCell ref="G54:G57"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="G36:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="G29:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="G16:G19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A75:A77"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
